--- a/Master.xlsx
+++ b/Master.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C707283D-9ACE-4AB8-BE0B-44605FFA5093}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97F46CC-2550-4058-B642-E9C17104194D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="42150" yWindow="2920" windowWidth="22230" windowHeight="14240" xr2:uid="{2C5B991D-6CD6-4A19-B904-248F473C2467}"/>
+    <workbookView xWindow="2930" yWindow="6310" windowWidth="22360" windowHeight="12770" xr2:uid="{2C5B991D-6CD6-4A19-B904-248F473C2467}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
   <si>
     <t>Healthcare</t>
   </si>
@@ -143,9 +143,6 @@
     <t>Games</t>
   </si>
   <si>
-    <t>Poker</t>
-  </si>
-  <si>
     <t>Biology</t>
   </si>
   <si>
@@ -153,12 +150,6 @@
   </si>
   <si>
     <t>Interactive Entertainment</t>
-  </si>
-  <si>
-    <t>Card Games (Non-Poker)</t>
-  </si>
-  <si>
-    <t>Games (Combinatorial)</t>
   </si>
   <si>
     <t>Hedge Funds</t>
@@ -659,7 +650,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D5" s="3">
         <v>45845</v>
@@ -677,18 +668,18 @@
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C6" s="2" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D6" s="3">
         <v>45691</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="G6" s="5"/>
       <c r="I6" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="J6" s="3">
         <v>45158</v>
@@ -706,7 +697,7 @@
       </c>
       <c r="G7" s="5"/>
       <c r="I7" s="2" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="J7" s="3">
         <v>45582</v>
@@ -740,13 +731,13 @@
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="4" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D10" s="3">
         <v>45718</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G10" s="3">
         <v>45754</v>
@@ -754,7 +745,7 @@
     </row>
     <row r="11" spans="2:10" ht="13" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D11" s="3">
         <v>45718</v>
@@ -782,7 +773,7 @@
       </c>
       <c r="G12" s="5"/>
       <c r="I12" s="2" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="J12" s="3">
         <v>45156</v>
@@ -802,7 +793,7 @@
         <v>45688</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="J13" s="3">
         <v>44955</v>
@@ -822,12 +813,12 @@
         <v>45754</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D15" s="3">
         <v>45591</v>
@@ -855,18 +846,21 @@
         <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="2" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C18" s="3">
         <v>44973</v>
       </c>
-      <c r="F18" t="s">
-        <v>39</v>
+      <c r="F18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G18" s="3">
+        <v>45040</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>33</v>
@@ -883,10 +877,10 @@
         <v>44943</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G19" s="3">
-        <v>45040</v>
+        <v>45157</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>17</v>
@@ -894,14 +888,11 @@
     </row>
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C20" s="3">
         <v>45717</v>
       </c>
-      <c r="F20" t="s">
-        <v>40</v>
-      </c>
       <c r="I20" s="2" t="s">
         <v>21</v>
       </c>
@@ -911,33 +902,24 @@
     </row>
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="2" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C21" s="3">
         <v>45803</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="G21" s="3">
-        <v>45157</v>
-      </c>
       <c r="I21" s="2" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C22" s="3">
         <v>45741</v>
       </c>
-      <c r="F22" t="s">
-        <v>35</v>
-      </c>
       <c r="I22" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="J22" s="3">
         <v>45657</v>
@@ -967,8 +949,8 @@
     <hyperlink ref="I13" r:id="rId20" xr:uid="{A65108F0-2E05-4701-9FD5-ECB4643B538C}"/>
     <hyperlink ref="F13" r:id="rId21" xr:uid="{80621359-2F8B-4A5B-BC6A-2FB82EA4769B}"/>
     <hyperlink ref="I16" r:id="rId22" xr:uid="{CD87D806-2453-46D8-B81F-88E0AF410576}"/>
-    <hyperlink ref="F21" r:id="rId23" xr:uid="{A3E39291-0AD8-4434-9956-506F6456A6EF}"/>
-    <hyperlink ref="F19" r:id="rId24" xr:uid="{3E303140-6F63-43CA-A742-BF4F34C477BF}"/>
+    <hyperlink ref="F19" r:id="rId23" xr:uid="{A3E39291-0AD8-4434-9956-506F6456A6EF}"/>
+    <hyperlink ref="F18" r:id="rId24" xr:uid="{3E303140-6F63-43CA-A742-BF4F34C477BF}"/>
     <hyperlink ref="B20" r:id="rId25" xr:uid="{94B54C11-D57C-4517-801E-20549E100878}"/>
     <hyperlink ref="B21" r:id="rId26" xr:uid="{548404B7-486D-4DC1-8702-5308F6B726F9}"/>
     <hyperlink ref="F4" r:id="rId27" xr:uid="{7461AF2B-1114-4E32-AB2C-C6FAFC7D3A58}"/>

--- a/Master.xlsx
+++ b/Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F97F46CC-2550-4058-B642-E9C17104194D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43AFA66B-7172-44D8-9725-2E02F1358910}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2930" yWindow="6310" windowWidth="22360" windowHeight="12770" xr2:uid="{2C5B991D-6CD6-4A19-B904-248F473C2467}"/>
+    <workbookView xWindow="4220" yWindow="4000" windowWidth="22360" windowHeight="16580" xr2:uid="{2C5B991D-6CD6-4A19-B904-248F473C2467}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -692,7 +692,7 @@
       <c r="D7" s="3">
         <v>45718</v>
       </c>
-      <c r="F7" t="s">
+      <c r="F7" s="2" t="s">
         <v>31</v>
       </c>
       <c r="G7" s="5"/>
@@ -970,8 +970,9 @@
     <hyperlink ref="I14" r:id="rId41" xr:uid="{58E30F9F-C4AC-49C0-954A-3705C3A32C26}"/>
     <hyperlink ref="F5" r:id="rId42" xr:uid="{CF731145-D908-4126-8E01-24EB9D7C30A7}"/>
     <hyperlink ref="B11" r:id="rId43" xr:uid="{FA315E08-E8F1-4B3E-950F-7F4D6698C736}"/>
+    <hyperlink ref="F7" r:id="rId44" xr:uid="{4CCFC45B-5161-43A2-8335-C0C03D0F0A4F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId44"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId45"/>
 </worksheet>
 </file>